--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Czech Republic First League_20242025.xlsx
@@ -18602,13 +18602,13 @@
         <v>7</v>
       </c>
       <c r="BA83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB83" t="n">
         <v>3</v>
       </c>
       <c r="BC83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD83" t="n">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Czech Republic First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Czech Republic First League_20242025.xlsx
@@ -59568,13 +59568,13 @@
         <v>3.7</v>
       </c>
       <c r="AU271" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW271" t="n">
         <v>10</v>
-      </c>
-      <c r="AV271" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW271" t="n">
-        <v>9</v>
       </c>
       <c r="AX271" t="n">
         <v>5</v>
@@ -59583,7 +59583,7 @@
         <v>19</v>
       </c>
       <c r="AZ271" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA271" t="n">
         <v>4</v>
@@ -59786,22 +59786,22 @@
         <v>2.93</v>
       </c>
       <c r="AU272" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV272" t="n">
         <v>4</v>
       </c>
       <c r="AW272" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX272" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY272" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ272" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA272" t="n">
         <v>3</v>
@@ -60004,22 +60004,22 @@
         <v>2.98</v>
       </c>
       <c r="AU273" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW273" t="n">
         <v>6</v>
       </c>
-      <c r="AV273" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW273" t="n">
-        <v>7</v>
-      </c>
       <c r="AX273" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY273" t="n">
         <v>10</v>
       </c>
-      <c r="AY273" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ273" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA273" t="n">
         <v>3</v>
@@ -60222,22 +60222,22 @@
         <v>2.62</v>
       </c>
       <c r="AU274" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW274" t="n">
         <v>4</v>
       </c>
       <c r="AX274" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY274" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ274" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ274" t="n">
-        <v>6</v>
       </c>
       <c r="BA274" t="n">
         <v>2</v>
@@ -60440,19 +60440,19 @@
         <v>2.38</v>
       </c>
       <c r="AU275" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV275" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW275" t="n">
         <v>5</v>
       </c>
       <c r="AX275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY275" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ275" t="n">
         <v>6</v>
@@ -60879,19 +60879,19 @@
         <v>5</v>
       </c>
       <c r="AV277" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW277" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX277" t="n">
         <v>7</v>
       </c>
-      <c r="AX277" t="n">
+      <c r="AY277" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ277" t="n">
         <v>10</v>
-      </c>
-      <c r="AY277" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ277" t="n">
-        <v>15</v>
       </c>
       <c r="BA277" t="n">
         <v>2</v>
